--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:48:09+00:00</t>
+    <t>2026-09-14T12:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:20:33+00:00</t>
+    <t>2026-09-14T12:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Genliste des Panels: Basic-NGS Panel (36 Gene). Kodiert als HGNC-Gensymbole; TODO:REVIEW HGNC-ID-Mapping.</t>
+    <t>Genliste des Panels: Basic-NGS Panel (36 Gene). Kodiert mit stabilen HGNC-IDs (System genenames.org/geneId), Displays = aktuelle HGNC-Symbole.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,111 +102,219 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>HGNC:391</t>
+  </si>
+  <si>
     <t>AKT1</t>
   </si>
   <si>
+    <t>HGNC:583</t>
+  </si>
+  <si>
     <t>APC</t>
   </si>
   <si>
+    <t>HGNC:950</t>
+  </si>
+  <si>
     <t>BAP1</t>
   </si>
   <si>
+    <t>HGNC:1097</t>
+  </si>
+  <si>
     <t>BRAF</t>
   </si>
   <si>
+    <t>HGNC:1100</t>
+  </si>
+  <si>
     <t>BRCA1</t>
   </si>
   <si>
+    <t>HGNC:1101</t>
+  </si>
+  <si>
     <t>BRCA2</t>
   </si>
   <si>
+    <t>HGNC:2514</t>
+  </si>
+  <si>
     <t>CTNNB1</t>
   </si>
   <si>
+    <t>HGNC:3236</t>
+  </si>
+  <si>
     <t>EGFR</t>
   </si>
   <si>
+    <t>HGNC:3430</t>
+  </si>
+  <si>
     <t>ERBB2</t>
   </si>
   <si>
+    <t>HGNC:3467</t>
+  </si>
+  <si>
     <t>ESR1</t>
   </si>
   <si>
+    <t>HGNC:3689</t>
+  </si>
+  <si>
     <t>FGFR2</t>
   </si>
   <si>
+    <t>HGNC:3690</t>
+  </si>
+  <si>
     <t>FGFR3</t>
   </si>
   <si>
+    <t>HGNC:4379</t>
+  </si>
+  <si>
     <t>GNA11</t>
   </si>
   <si>
+    <t>HGNC:4390</t>
+  </si>
+  <si>
     <t>GNAQ</t>
   </si>
   <si>
+    <t>HGNC:4392</t>
+  </si>
+  <si>
     <t>GNAS</t>
   </si>
   <si>
+    <t>HGNC:5173</t>
+  </si>
+  <si>
     <t>HRAS</t>
   </si>
   <si>
+    <t>HGNC:5382</t>
+  </si>
+  <si>
     <t>IDH1</t>
   </si>
   <si>
+    <t>HGNC:5383</t>
+  </si>
+  <si>
     <t>IDH2</t>
   </si>
   <si>
+    <t>HGNC:6342</t>
+  </si>
+  <si>
     <t>KIT</t>
   </si>
   <si>
+    <t>HGNC:6407</t>
+  </si>
+  <si>
     <t>KRAS</t>
   </si>
   <si>
+    <t>HGNC:7029</t>
+  </si>
+  <si>
     <t>MET</t>
   </si>
   <si>
+    <t>HGNC:7127</t>
+  </si>
+  <si>
     <t>MLH1</t>
   </si>
   <si>
+    <t>HGNC:7325</t>
+  </si>
+  <si>
     <t>MSH2</t>
   </si>
   <si>
+    <t>HGNC:7329</t>
+  </si>
+  <si>
     <t>MSH6</t>
   </si>
   <si>
+    <t>HGNC:7989</t>
+  </si>
+  <si>
     <t>NRAS</t>
   </si>
   <si>
+    <t>HGNC:26144</t>
+  </si>
+  <si>
     <t>PALB2</t>
   </si>
   <si>
+    <t>HGNC:8803</t>
+  </si>
+  <si>
     <t>PDGFRA</t>
   </si>
   <si>
+    <t>HGNC:8975</t>
+  </si>
+  <si>
     <t>PIK3CA</t>
   </si>
   <si>
+    <t>HGNC:9122</t>
+  </si>
+  <si>
     <t>PMS2</t>
   </si>
   <si>
+    <t>HGNC:9177</t>
+  </si>
+  <si>
     <t>POLE</t>
   </si>
   <si>
+    <t>HGNC:9588</t>
+  </si>
+  <si>
     <t>PTEN</t>
   </si>
   <si>
+    <t>HGNC:9884</t>
+  </si>
+  <si>
     <t>RB1</t>
   </si>
   <si>
+    <t>HGNC:9967</t>
+  </si>
+  <si>
     <t>RET</t>
   </si>
   <si>
+    <t>HGNC:11100</t>
+  </si>
+  <si>
     <t>SMARCA4</t>
   </si>
   <si>
+    <t>HGNC:11730</t>
+  </si>
+  <si>
     <t>TERT</t>
   </si>
   <si>
+    <t>HGNC:11998</t>
+  </si>
+  <si>
     <t>TP53</t>
   </si>
   <si>
@@ -216,7 +324,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://www.genenames.org</t>
+    <t>http://www.genenames.org/geneId</t>
   </si>
 </sst>
 </file>
@@ -500,303 +608,303 @@
         <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>50</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>53</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>57</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>61</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>65</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>67</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:53:39+00:00</t>
+    <t>2026-09-14T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-basic-ngs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:42:50+00:00</t>
+    <t>2026-09-14T17:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
